--- a/Week2/day1/ExerciceXP/mon_dataframe.xlsx
+++ b/Week2/day1/ExerciceXP/mon_dataframe.xlsx
@@ -424,12 +424,12 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Age</t>
+          <t>Âge</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Profession</t>
+          <t>Langage</t>
         </is>
       </c>
     </row>
@@ -444,7 +444,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ingénieur</t>
+          <t>Python</t>
         </is>
       </c>
     </row>
@@ -459,7 +459,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Médecin</t>
+          <t>JavaScript</t>
         </is>
       </c>
     </row>
@@ -474,7 +474,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Analyste</t>
+          <t>C++</t>
         </is>
       </c>
     </row>
